--- a/outputs/rebalancing_predictions.xlsx
+++ b/outputs/rebalancing_predictions.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1022,6 +1022,27 @@
         <v>0</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="14" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Mar/Sep (general review)</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="n"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1034,14 +1055,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="43" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
@@ -1105,6 +1126,767 @@
         <is>
           <t>Confidence Depth %</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Mar/Sep (general review)</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>WELCORP</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Welspun Corp Ltd.</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>159</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>254.5</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>70171</v>
+      </c>
+      <c r="J2" s="8" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="n">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Mar/Sep (general review)</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>ASTERDM</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Aster DM Healthcare Ltd.</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>167</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>65816</v>
+      </c>
+      <c r="J3" s="8" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Mar/Sep (general review)</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Ather Energy Ltd.</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>171</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>64697</v>
+      </c>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Mar/Sep (general review)</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>RADICO</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Radico Khaitan Ltd</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>186</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>277.8</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>58684</v>
+      </c>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Mar/Sep (general review)</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>ABBOTINDIA</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Abbott India Ltd.</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>189</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>198.9</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>55514</v>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Mar/Sep (general review)</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>ANTHEM</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Anthem Biosciences Ltd.</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>192</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>52312</v>
+      </c>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Mar/Sep (general review)</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>AEGISLOG</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Aegis Logistics Ltd.</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>204</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>364.3</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>49681</v>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Mar/Sep (general review)</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>FACT</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Fertilisers and Chemicals Travancore Ltd.</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>205</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>376.1</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>49449</v>
+      </c>
+      <c r="J9" s="8" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Mar/Sep (general review)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>GLAND</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Gland Pharma Ltd.</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>206</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>48861</v>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Mar/Sep (general review)</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>NAVINFLUOR</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Navin Fluorine International Ltd.</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>216</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>230.3</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>44053</v>
+      </c>
+      <c r="J11" s="8" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Mar/Sep (general review)</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>MEDANTA</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Global Health Ltd.</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>226</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>40315</v>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Mar/Sep (general review)</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>CPPLUS</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Aditya Infotech Ltd.</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>228</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>39691</v>
+      </c>
+      <c r="J13" s="8" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Mar/Sep (general review)</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>PWL</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Physicswallah Ltd.</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>229</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>39626</v>
+      </c>
+      <c r="J14" s="8" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Mar/Sep (general review)</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>KPRMILL</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>K.P.R. Mill Ltd.</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>235</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>227.4</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>38331</v>
+      </c>
+      <c r="J15" s="8" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Mar/Sep (general review)</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>EMCURE</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Emcure Pharmaceuticals Ltd.</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>237</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>87.59999999999999</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>38008</v>
+      </c>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Mar/Sep (general review)</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Remove</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>BATAINDIA</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Bata India Ltd.</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>487</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="n">
+        <v>8204</v>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>91.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Mar/Sep (general review)</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Remove</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>WHIRLPOOL</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Whirlpool of India Ltd.</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>476</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="5" t="n">
+        <v>9229</v>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>79.5</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/rebalancing_predictions.xlsx
+++ b/outputs/rebalancing_predictions.xlsx
@@ -1032,13 +1032,13 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D17" s="5" t="n"/>
       <c r="E17" s="5" t="n"/>
       <c r="F17" s="5" t="n"/>
       <c r="G17" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H17" s="5" t="n"/>
       <c r="I17" s="5" t="n"/>
@@ -1055,7 +1055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1153,16 +1153,16 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>77.59999999999999</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="H2" s="5" t="n">
         <v>254.5</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>70171</v>
+        <v>68739</v>
       </c>
       <c r="J2" s="8" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="K2" s="5" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="3">
@@ -1198,16 +1198,16 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>78.90000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="H3" s="5" t="n">
         <v>101.2</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>65816</v>
+        <v>61793</v>
       </c>
       <c r="J3" s="8" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="K3" s="5" t="n">
-        <v>10.3</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -1234,25 +1234,25 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>ABBOTINDIA</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Ather Energy Ltd.</t>
+          <t>Abbott India Ltd.</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>79.59999999999999</v>
+        <v>81</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>14.8</v>
+        <v>198.9</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>64697</v>
+        <v>57033</v>
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="K4" s="5" t="n">
-        <v>9.6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -1288,16 +1288,16 @@
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>81.8</v>
+        <v>81.3</v>
       </c>
       <c r="H5" s="5" t="n">
         <v>277.8</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>58684</v>
+        <v>56768</v>
       </c>
       <c r="J5" s="8" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="K5" s="5" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="6">
@@ -1324,25 +1324,25 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>ABBOTINDIA</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Abbott India Ltd.</t>
+          <t>Ather Energy Ltd.</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>82.2</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>198.9</v>
+        <v>14.8</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>55514</v>
+        <v>55470</v>
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="7">
@@ -1369,25 +1369,25 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>ANTHEM</t>
+          <t>AEGISLOG</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Anthem Biosciences Ltd.</t>
+          <t>Aegis Logistics Ltd.</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>82.59999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>12.3</v>
+        <v>364.3</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>52312</v>
+        <v>49179</v>
       </c>
       <c r="J7" s="8" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="8">
@@ -1414,25 +1414,25 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>AEGISLOG</t>
+          <t>ANTHEM</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Aegis Logistics Ltd.</t>
+          <t>Anthem Biosciences Ltd.</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>84.09999999999999</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>364.3</v>
+        <v>12.3</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>49681</v>
+        <v>48214</v>
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="9">
@@ -1468,16 +1468,16 @@
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>84.2</v>
+        <v>83.7</v>
       </c>
       <c r="H9" s="5" t="n">
         <v>376.1</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>49449</v>
+        <v>47557</v>
       </c>
       <c r="J9" s="8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="10">
@@ -1513,16 +1513,16 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>84.40000000000001</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="H10" s="5" t="n">
         <v>68.40000000000001</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>48861</v>
+        <v>47418</v>
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="11">
@@ -1549,25 +1549,25 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>NAVINFLUOR</t>
+          <t>CPPLUS</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Navin Fluorine International Ltd.</t>
+          <t>Aditya Infotech Ltd.</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>85.5</v>
+        <v>84.8</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>230.3</v>
+        <v>11.8</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>44053</v>
+        <v>44949</v>
       </c>
       <c r="J11" s="8" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="K11" s="5" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="12">
@@ -1594,25 +1594,25 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>MEDANTA</t>
+          <t>NAVINFLUOR</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Global Health Ltd.</t>
+          <t>Navin Fluorine International Ltd.</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>86.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>44.5</v>
+        <v>230.3</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>40315</v>
+        <v>41727</v>
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="13">
@@ -1639,25 +1639,25 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>CPPLUS</t>
+          <t>EMCURE</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Aditya Infotech Ltd.</t>
+          <t>Emcure Pharmaceuticals Ltd.</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>86.7</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>11.8</v>
+        <v>24.7</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>39691</v>
+        <v>36885</v>
       </c>
       <c r="J13" s="8" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="14">
@@ -1684,25 +1684,25 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>PWL</t>
+          <t>KPRMILL</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Physicswallah Ltd.</t>
+          <t>K.P.R. Mill Ltd.</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>86.8</v>
+        <v>87</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>8.4</v>
+        <v>227.4</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>39626</v>
+        <v>36608</v>
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="15">
@@ -1729,25 +1729,25 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>KPRMILL</t>
+          <t>MEDANTA</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>K.P.R. Mill Ltd.</t>
+          <t>Global Health Ltd.</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>87.40000000000001</v>
+        <v>87.2</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>227.4</v>
+        <v>44.5</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>38331</v>
+        <v>36494</v>
       </c>
       <c r="J15" s="8" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="16">
@@ -1774,25 +1774,25 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>EMCURE</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Emcure Pharmaceuticals Ltd.</t>
+          <t>HFCL Ltd.</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>87.59999999999999</v>
+        <v>87.3</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>24.7</v>
+        <v>185</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>38008</v>
+        <v>36483</v>
       </c>
       <c r="J16" s="8" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="17">
@@ -1814,36 +1814,38 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Remove</t>
+          <t>Add</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>BATAINDIA</t>
+          <t>ANANDRATHI</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Bata India Ltd.</t>
+          <t>Anand Rathi Wealth Ltd.</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>487</v>
+        <v>239</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>99.8</v>
-      </c>
-      <c r="H17" s="5" t="n"/>
+        <v>87.7</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>55.6</v>
+      </c>
       <c r="I17" s="5" t="n">
-        <v>8204</v>
-      </c>
-      <c r="J17" s="7" t="inlineStr">
-        <is>
-          <t>High</t>
+        <v>35159</v>
+      </c>
+      <c r="J17" s="8" t="inlineStr">
+        <is>
+          <t>Watch</t>
         </is>
       </c>
       <c r="K17" s="5" t="n">
-        <v>91.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="18">
@@ -1857,36 +1859,167 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>PWL</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Physicswallah Ltd.</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>241</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>34860</v>
+      </c>
+      <c r="J18" s="8" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Mar/Sep (general review)</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
           <t>Remove</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>BATAINDIA</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Bata India Ltd.</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>488</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="5" t="n">
+        <v>7879</v>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>92.2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Mar/Sep (general review)</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Remove</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>WHIRLPOOL</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>Whirlpool of India Ltd.</t>
         </is>
       </c>
-      <c r="F18" s="5" t="n">
-        <v>476</v>
-      </c>
-      <c r="G18" s="5" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="n">
-        <v>9229</v>
-      </c>
-      <c r="J18" s="7" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K18" s="5" t="n">
-        <v>79.5</v>
+      <c r="F20" s="5" t="n">
+        <v>447</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="n">
+        <v>10932</v>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>Elevated</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>43.7</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Mar/Sep (general review)</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Remove</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>KPITTECH</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>KPIT Technologies Ltd.</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>420</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>98</v>
+      </c>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="5" t="n">
+        <v>13488</v>
+      </c>
+      <c r="J21" s="8" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>1.7</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/rebalancing_predictions.xlsx
+++ b/outputs/rebalancing_predictions.xlsx
@@ -1038,7 +1038,7 @@
       <c r="E17" s="5" t="n"/>
       <c r="F17" s="5" t="n"/>
       <c r="G17" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H17" s="5" t="n"/>
       <c r="I17" s="5" t="n"/>
@@ -1055,7 +1055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1153,16 +1153,16 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>76.40000000000001</v>
+        <v>76.5</v>
       </c>
       <c r="H2" s="5" t="n">
         <v>254.5</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>68739</v>
+        <v>68398</v>
       </c>
       <c r="J2" s="8" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="K2" s="5" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="3">
@@ -1189,25 +1189,25 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>ASTERDM</t>
+          <t>RADICO</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Aster DM Healthcare Ltd.</t>
+          <t>Radico Khaitan Ltd</t>
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>79.5</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>101.2</v>
+        <v>277.8</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>61793</v>
+        <v>59428</v>
       </c>
       <c r="J3" s="8" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="K3" s="5" t="n">
-        <v>9.699999999999999</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="4">
@@ -1234,25 +1234,25 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>ABBOTINDIA</t>
+          <t>ASTERDM</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Abbott India Ltd.</t>
+          <t>Aster DM Healthcare Ltd.</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>81</v>
+        <v>80.7</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>198.9</v>
+        <v>101.2</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>57033</v>
+        <v>58154</v>
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="K4" s="5" t="n">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -1279,25 +1279,25 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>RADICO</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Radico Khaitan Ltd</t>
+          <t>Ather Energy Ltd.</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>81.3</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>277.8</v>
+        <v>14.8</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>56768</v>
+        <v>57557</v>
       </c>
       <c r="J5" s="8" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="K5" s="5" t="n">
-        <v>7.6</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="6">
@@ -1324,25 +1324,25 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>ABBOTINDIA</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Ather Energy Ltd.</t>
+          <t>Abbott India Ltd.</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>81.40000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>14.8</v>
+        <v>198.9</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>55470</v>
+        <v>55046</v>
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -1369,25 +1369,25 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>AEGISLOG</t>
+          <t>GLAND</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Aegis Logistics Ltd.</t>
+          <t>Gland Pharma Ltd.</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>82.90000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>364.3</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>49179</v>
+        <v>49817</v>
       </c>
       <c r="J7" s="8" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="8">
@@ -1414,25 +1414,25 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>ANTHEM</t>
+          <t>CPPLUS</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Anthem Biosciences Ltd.</t>
+          <t>Aditya Infotech Ltd.</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>83.09999999999999</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>12.3</v>
+        <v>11.8</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>48214</v>
+        <v>47438</v>
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -1471,13 +1471,13 @@
         <v>201</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>83.7</v>
+        <v>84</v>
       </c>
       <c r="H9" s="5" t="n">
         <v>376.1</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>47557</v>
+        <v>46803</v>
       </c>
       <c r="J9" s="8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="10">
@@ -1504,25 +1504,25 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>GLAND</t>
+          <t>AEGISLOG</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Gland Pharma Ltd.</t>
+          <t>Aegis Logistics Ltd.</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
         <v>202</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>83.90000000000001</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>68.40000000000001</v>
+        <v>364.3</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>47418</v>
+        <v>46746</v>
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="11">
@@ -1549,25 +1549,25 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>CPPLUS</t>
+          <t>ANTHEM</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Aditya Infotech Ltd.</t>
+          <t>Anthem Biosciences Ltd.</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>84.8</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>11.8</v>
+        <v>12.3</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>44949</v>
+        <v>45552</v>
       </c>
       <c r="J11" s="8" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="K11" s="5" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="12">
@@ -1603,16 +1603,16 @@
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>85.90000000000001</v>
+        <v>86</v>
       </c>
       <c r="H12" s="5" t="n">
         <v>230.3</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>41727</v>
+        <v>41810</v>
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="13">
@@ -1639,25 +1639,25 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>EMCURE</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Emcure Pharmaceuticals Ltd.</t>
+          <t>HFCL Ltd.</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>86.90000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>24.7</v>
+        <v>185</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>36885</v>
+        <v>41144</v>
       </c>
       <c r="J13" s="8" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="14">
@@ -1684,25 +1684,25 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>KPRMILL</t>
+          <t>PWL</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>K.P.R. Mill Ltd.</t>
+          <t>Physicswallah Ltd.</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>87</v>
+        <v>87.3</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>227.4</v>
+        <v>8.4</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>36608</v>
+        <v>37717</v>
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="15">
@@ -1729,25 +1729,25 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>MEDANTA</t>
+          <t>PTCIL</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Global Health Ltd.</t>
+          <t>PTC Industries Ltd.</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>87.2</v>
+        <v>87.5</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>44.5</v>
+        <v>37.8</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>36494</v>
+        <v>37549</v>
       </c>
       <c r="J15" s="8" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="16">
@@ -1774,25 +1774,25 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>KPRMILL</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>HFCL Ltd.</t>
+          <t>K.P.R. Mill Ltd.</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>87.3</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>185</v>
+        <v>227.4</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>36483</v>
+        <v>36557</v>
       </c>
       <c r="J16" s="8" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="17">
@@ -1828,16 +1828,16 @@
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>87.7</v>
+        <v>87.8</v>
       </c>
       <c r="H17" s="5" t="n">
         <v>55.6</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>35159</v>
+        <v>35930</v>
       </c>
       <c r="J17" s="8" t="inlineStr">
         <is>
@@ -1864,25 +1864,25 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>PWL</t>
+          <t>KARURVYSYA</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Physicswallah Ltd.</t>
+          <t>Karur Vysya Bank Ltd.</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>87.90000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>8.4</v>
+        <v>312.5</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>34860</v>
+        <v>35768</v>
       </c>
       <c r="J18" s="8" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="19">
@@ -1918,14 +1918,14 @@
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>99.8</v>
+        <v>99.7</v>
       </c>
       <c r="H19" s="5" t="n"/>
       <c r="I19" s="5" t="n">
-        <v>7879</v>
+        <v>8169</v>
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         </is>
       </c>
       <c r="K19" s="5" t="n">
-        <v>92.2</v>
+        <v>86.40000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -1961,14 +1961,14 @@
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="G20" s="5" t="n">
         <v>98.90000000000001</v>
       </c>
       <c r="H20" s="5" t="n"/>
       <c r="I20" s="5" t="n">
-        <v>10932</v>
+        <v>10641</v>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
@@ -1976,50 +1976,7 @@
         </is>
       </c>
       <c r="K20" s="5" t="n">
-        <v>43.7</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="14" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Mar/Sep (general review)</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Remove</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>KPITTECH</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>KPIT Technologies Ltd.</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="n">
-        <v>420</v>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>98</v>
-      </c>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="5" t="n">
-        <v>13488</v>
-      </c>
-      <c r="J21" s="8" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="n">
-        <v>1.7</v>
+        <v>47.4</v>
       </c>
     </row>
   </sheetData>
